--- a/artfynd/A 32741-2025 artfynd.xlsx
+++ b/artfynd/A 32741-2025 artfynd.xlsx
@@ -675,48 +675,58 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127096398</v>
+        <v>127098060</v>
       </c>
       <c r="B2" t="n">
-        <v>78980</v>
+        <v>98457</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529736</v>
+        <v>529843</v>
       </c>
       <c r="R2" t="n">
-        <v>6999860</v>
+        <v>6999863</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,11 +753,21 @@
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -760,26 +780,6 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,55 +797,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127098060</v>
+        <v>127098716</v>
       </c>
       <c r="B3" t="n">
-        <v>98382</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529843</v>
+        <v>529925</v>
       </c>
       <c r="R3" t="n">
-        <v>6999863</v>
+        <v>6999898</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -877,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,6 +897,26 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -919,10 +934,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127098716</v>
+        <v>127096398</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -954,13 +969,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529925</v>
+        <v>529736</v>
       </c>
       <c r="R4" t="n">
-        <v>6999898</v>
+        <v>6999860</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,24 +1002,9 @@
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1059,7 +1059,7 @@
         <v>127098468</v>
       </c>
       <c r="B5" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>127099015</v>
       </c>
       <c r="B6" t="n">
-        <v>98382</v>
+        <v>98457</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>127098756</v>
       </c>
       <c r="B7" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>127097774</v>
       </c>
       <c r="B8" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>127098449</v>
       </c>
       <c r="B9" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>127096776</v>
       </c>
       <c r="B10" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>127099425</v>
       </c>
       <c r="B11" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127172686</v>
+        <v>127172688</v>
       </c>
       <c r="B12" t="n">
         <v>57817</v>
@@ -2008,10 +2008,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529974</v>
+        <v>530008</v>
       </c>
       <c r="R12" t="n">
-        <v>6999891</v>
+        <v>6999777</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2070,7 +2070,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127172688</v>
+        <v>127172686</v>
       </c>
       <c r="B13" t="n">
         <v>57817</v>
@@ -2105,10 +2105,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>530008</v>
+        <v>529974</v>
       </c>
       <c r="R13" t="n">
-        <v>6999777</v>
+        <v>6999891</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2170,7 +2170,7 @@
         <v>127172695</v>
       </c>
       <c r="B14" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>127172679</v>
       </c>
       <c r="B15" t="n">
-        <v>96614</v>
+        <v>96689</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>127172694</v>
       </c>
       <c r="B16" t="n">
-        <v>78738</v>
+        <v>78769</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>127172682</v>
       </c>
       <c r="B17" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>127172691</v>
       </c>
       <c r="B19" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2762,10 +2762,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127172700</v>
+        <v>127172689</v>
       </c>
       <c r="B20" t="n">
-        <v>78980</v>
+        <v>57817</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2773,21 +2773,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2797,10 +2797,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>530029</v>
+        <v>529921</v>
       </c>
       <c r="R20" t="n">
-        <v>6999789</v>
+        <v>6999851</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2859,10 +2859,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127172698</v>
+        <v>127172700</v>
       </c>
       <c r="B21" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2894,10 +2894,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529927</v>
+        <v>530029</v>
       </c>
       <c r="R21" t="n">
-        <v>6999903</v>
+        <v>6999789</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2956,10 +2956,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127172689</v>
+        <v>127172698</v>
       </c>
       <c r="B22" t="n">
-        <v>57817</v>
+        <v>79011</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2967,21 +2967,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529921</v>
+        <v>529927</v>
       </c>
       <c r="R22" t="n">
-        <v>6999851</v>
+        <v>6999903</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3053,32 +3053,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127172678</v>
+        <v>127172696</v>
       </c>
       <c r="B23" t="n">
-        <v>75075</v>
+        <v>98436</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>529804</v>
+        <v>530028</v>
       </c>
       <c r="R23" t="n">
-        <v>6999861</v>
+        <v>6999912</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3150,32 +3150,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127172696</v>
+        <v>127172678</v>
       </c>
       <c r="B24" t="n">
-        <v>98361</v>
+        <v>75135</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>530028</v>
+        <v>529804</v>
       </c>
       <c r="R24" t="n">
-        <v>6999912</v>
+        <v>6999861</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3360,7 +3360,7 @@
         <v>127172697</v>
       </c>
       <c r="B26" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>127172692</v>
       </c>
       <c r="B28" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3648,10 +3648,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127172693</v>
+        <v>127172680</v>
       </c>
       <c r="B29" t="n">
-        <v>78738</v>
+        <v>91319</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3659,21 +3659,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3683,10 +3683,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529977</v>
+        <v>529987</v>
       </c>
       <c r="R29" t="n">
-        <v>6999869</v>
+        <v>6999807</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3745,10 +3745,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127172680</v>
+        <v>127172693</v>
       </c>
       <c r="B30" t="n">
-        <v>91245</v>
+        <v>78769</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3756,21 +3756,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529987</v>
+        <v>529977</v>
       </c>
       <c r="R30" t="n">
-        <v>6999807</v>
+        <v>6999869</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3845,7 +3845,7 @@
         <v>127172701</v>
       </c>
       <c r="B31" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>127172681</v>
       </c>
       <c r="B32" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>127172699</v>
       </c>
       <c r="B33" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 32741-2025 artfynd.xlsx
+++ b/artfynd/A 32741-2025 artfynd.xlsx
@@ -675,55 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127098060</v>
+        <v>127098716</v>
       </c>
       <c r="B2" t="n">
-        <v>98457</v>
+        <v>79014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529843</v>
+        <v>529925</v>
       </c>
       <c r="R2" t="n">
-        <v>6999863</v>
+        <v>6999898</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
@@ -755,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,6 +775,26 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127098716</v>
+        <v>127096398</v>
       </c>
       <c r="B3" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,13 +847,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529925</v>
+        <v>529736</v>
       </c>
       <c r="R3" t="n">
-        <v>6999898</v>
+        <v>6999860</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,24 +880,9 @@
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,48 +934,58 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127096398</v>
+        <v>127098060</v>
       </c>
       <c r="B4" t="n">
-        <v>79011</v>
+        <v>98463</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529736</v>
+        <v>529843</v>
       </c>
       <c r="R4" t="n">
-        <v>6999860</v>
+        <v>6999863</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1002,11 +1012,21 @@
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1019,26 +1039,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1059,7 +1059,7 @@
         <v>127098468</v>
       </c>
       <c r="B5" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>127099015</v>
       </c>
       <c r="B6" t="n">
-        <v>98457</v>
+        <v>98463</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>127098756</v>
       </c>
       <c r="B7" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>127097774</v>
       </c>
       <c r="B8" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>127098449</v>
       </c>
       <c r="B9" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>127096776</v>
       </c>
       <c r="B10" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>127099425</v>
       </c>
       <c r="B11" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2167,32 +2167,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127172695</v>
+        <v>127172679</v>
       </c>
       <c r="B14" t="n">
-        <v>98436</v>
+        <v>96695</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529980</v>
+        <v>530000</v>
       </c>
       <c r="R14" t="n">
-        <v>6999916</v>
+        <v>6999721</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2264,32 +2264,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127172679</v>
+        <v>127172695</v>
       </c>
       <c r="B15" t="n">
-        <v>96689</v>
+        <v>98442</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>530000</v>
+        <v>529980</v>
       </c>
       <c r="R15" t="n">
-        <v>6999721</v>
+        <v>6999916</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2364,7 +2364,7 @@
         <v>127172694</v>
       </c>
       <c r="B16" t="n">
-        <v>78769</v>
+        <v>78772</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>127172682</v>
       </c>
       <c r="B17" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>127172691</v>
       </c>
       <c r="B19" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2762,10 +2762,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127172689</v>
+        <v>127172698</v>
       </c>
       <c r="B20" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2773,21 +2773,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2797,10 +2797,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529921</v>
+        <v>529927</v>
       </c>
       <c r="R20" t="n">
-        <v>6999851</v>
+        <v>6999903</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2862,7 +2862,7 @@
         <v>127172700</v>
       </c>
       <c r="B21" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2956,10 +2956,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127172698</v>
+        <v>127172689</v>
       </c>
       <c r="B22" t="n">
-        <v>79011</v>
+        <v>57817</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2967,21 +2967,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529927</v>
+        <v>529921</v>
       </c>
       <c r="R22" t="n">
-        <v>6999903</v>
+        <v>6999851</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3053,32 +3053,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127172696</v>
+        <v>127172678</v>
       </c>
       <c r="B23" t="n">
-        <v>98436</v>
+        <v>75138</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>530028</v>
+        <v>529804</v>
       </c>
       <c r="R23" t="n">
-        <v>6999912</v>
+        <v>6999861</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3150,32 +3150,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127172678</v>
+        <v>127172696</v>
       </c>
       <c r="B24" t="n">
-        <v>75135</v>
+        <v>98442</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529804</v>
+        <v>530028</v>
       </c>
       <c r="R24" t="n">
-        <v>6999861</v>
+        <v>6999912</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3357,32 +3357,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127172697</v>
+        <v>127172687</v>
       </c>
       <c r="B26" t="n">
-        <v>98436</v>
+        <v>57817</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>530041</v>
+        <v>530040</v>
       </c>
       <c r="R26" t="n">
-        <v>6999921</v>
+        <v>6999850</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3454,32 +3454,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127172687</v>
+        <v>127172697</v>
       </c>
       <c r="B27" t="n">
-        <v>57817</v>
+        <v>98442</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>530040</v>
+        <v>530041</v>
       </c>
       <c r="R27" t="n">
-        <v>6999850</v>
+        <v>6999921</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3554,7 +3554,7 @@
         <v>127172692</v>
       </c>
       <c r="B28" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>127172680</v>
       </c>
       <c r="B29" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>127172693</v>
       </c>
       <c r="B30" t="n">
-        <v>78769</v>
+        <v>78772</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>127172701</v>
       </c>
       <c r="B31" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>127172681</v>
       </c>
       <c r="B32" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>127172699</v>
       </c>
       <c r="B33" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 32741-2025 artfynd.xlsx
+++ b/artfynd/A 32741-2025 artfynd.xlsx
@@ -2167,32 +2167,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127172679</v>
+        <v>127172695</v>
       </c>
       <c r="B14" t="n">
-        <v>96695</v>
+        <v>98442</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>530000</v>
+        <v>529980</v>
       </c>
       <c r="R14" t="n">
-        <v>6999721</v>
+        <v>6999916</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2264,32 +2264,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127172695</v>
+        <v>127172679</v>
       </c>
       <c r="B15" t="n">
-        <v>98442</v>
+        <v>96695</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529980</v>
+        <v>530000</v>
       </c>
       <c r="R15" t="n">
-        <v>6999916</v>
+        <v>6999721</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2762,7 +2762,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127172698</v>
+        <v>127172700</v>
       </c>
       <c r="B20" t="n">
         <v>79014</v>
@@ -2797,10 +2797,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529927</v>
+        <v>530029</v>
       </c>
       <c r="R20" t="n">
-        <v>6999903</v>
+        <v>6999789</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2859,7 +2859,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127172700</v>
+        <v>127172698</v>
       </c>
       <c r="B21" t="n">
         <v>79014</v>
@@ -2894,10 +2894,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>530029</v>
+        <v>529927</v>
       </c>
       <c r="R21" t="n">
-        <v>6999789</v>
+        <v>6999903</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3053,32 +3053,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127172678</v>
+        <v>127172696</v>
       </c>
       <c r="B23" t="n">
-        <v>75138</v>
+        <v>98442</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>529804</v>
+        <v>530028</v>
       </c>
       <c r="R23" t="n">
-        <v>6999861</v>
+        <v>6999912</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3150,32 +3150,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127172696</v>
+        <v>127172678</v>
       </c>
       <c r="B24" t="n">
-        <v>98442</v>
+        <v>75138</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>530028</v>
+        <v>529804</v>
       </c>
       <c r="R24" t="n">
-        <v>6999912</v>
+        <v>6999861</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3247,53 +3247,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127172684</v>
+        <v>127172697</v>
       </c>
       <c r="B25" t="n">
-        <v>57657</v>
+        <v>98442</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Södra Rörmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>530054</v>
+        <v>530041</v>
       </c>
       <c r="R25" t="n">
-        <v>6999817</v>
+        <v>6999921</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3326,11 +3318,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3357,10 +3344,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127172687</v>
+        <v>127172684</v>
       </c>
       <c r="B26" t="n">
-        <v>57817</v>
+        <v>57657</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3368,34 +3355,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Södra Rörmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>530040</v>
+        <v>530054</v>
       </c>
       <c r="R26" t="n">
-        <v>6999850</v>
+        <v>6999817</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3428,6 +3423,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3454,32 +3454,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127172697</v>
+        <v>127172687</v>
       </c>
       <c r="B27" t="n">
-        <v>98442</v>
+        <v>57817</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>530041</v>
+        <v>530040</v>
       </c>
       <c r="R27" t="n">
-        <v>6999921</v>
+        <v>6999850</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3648,10 +3648,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127172680</v>
+        <v>127172693</v>
       </c>
       <c r="B29" t="n">
-        <v>91325</v>
+        <v>78772</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3659,21 +3659,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3683,10 +3683,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529987</v>
+        <v>529977</v>
       </c>
       <c r="R29" t="n">
-        <v>6999807</v>
+        <v>6999869</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3745,10 +3745,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127172693</v>
+        <v>127172680</v>
       </c>
       <c r="B30" t="n">
-        <v>78772</v>
+        <v>91325</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3756,21 +3756,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529977</v>
+        <v>529987</v>
       </c>
       <c r="R30" t="n">
-        <v>6999869</v>
+        <v>6999807</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3939,10 +3939,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127172681</v>
+        <v>127172699</v>
       </c>
       <c r="B32" t="n">
-        <v>91325</v>
+        <v>79014</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3950,21 +3950,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3974,10 +3974,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>529827</v>
+        <v>530016</v>
       </c>
       <c r="R32" t="n">
-        <v>6999866</v>
+        <v>6999865</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4036,10 +4036,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127172699</v>
+        <v>127172681</v>
       </c>
       <c r="B33" t="n">
-        <v>79014</v>
+        <v>91325</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4047,21 +4047,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4071,10 +4071,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>530016</v>
+        <v>529827</v>
       </c>
       <c r="R33" t="n">
-        <v>6999865</v>
+        <v>6999866</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 32741-2025 artfynd.xlsx
+++ b/artfynd/A 32741-2025 artfynd.xlsx
@@ -675,45 +675,55 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127098716</v>
+        <v>127098060</v>
       </c>
       <c r="B2" t="n">
-        <v>79014</v>
+        <v>98463</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529925</v>
+        <v>529843</v>
       </c>
       <c r="R2" t="n">
-        <v>6999898</v>
+        <v>6999863</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
@@ -745,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,26 +780,6 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -812,7 +797,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127096398</v>
+        <v>127098716</v>
       </c>
       <c r="B3" t="n">
         <v>79014</v>
@@ -847,13 +832,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529736</v>
+        <v>529925</v>
       </c>
       <c r="R3" t="n">
-        <v>6999860</v>
+        <v>6999898</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,9 +865,24 @@
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,58 +934,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127098060</v>
+        <v>127096398</v>
       </c>
       <c r="B4" t="n">
-        <v>98463</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529843</v>
+        <v>529736</v>
       </c>
       <c r="R4" t="n">
-        <v>6999863</v>
+        <v>6999860</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,21 +1002,11 @@
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1039,6 +1019,26 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 32741-2025 artfynd.xlsx
+++ b/artfynd/A 32741-2025 artfynd.xlsx
@@ -675,55 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127098060</v>
+        <v>127098716</v>
       </c>
       <c r="B2" t="n">
-        <v>98463</v>
+        <v>79014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529843</v>
+        <v>529925</v>
       </c>
       <c r="R2" t="n">
-        <v>6999863</v>
+        <v>6999898</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
@@ -755,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,6 +775,26 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,7 +812,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127098716</v>
+        <v>127096398</v>
       </c>
       <c r="B3" t="n">
         <v>79014</v>
@@ -832,13 +847,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529925</v>
+        <v>529736</v>
       </c>
       <c r="R3" t="n">
-        <v>6999898</v>
+        <v>6999860</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,24 +880,9 @@
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,48 +934,58 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127096398</v>
+        <v>127098060</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>98464</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529736</v>
+        <v>529843</v>
       </c>
       <c r="R4" t="n">
-        <v>6999860</v>
+        <v>6999863</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1002,11 +1012,21 @@
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1019,26 +1039,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1181,7 +1181,7 @@
         <v>127099015</v>
       </c>
       <c r="B6" t="n">
-        <v>98463</v>
+        <v>98464</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>127097774</v>
       </c>
       <c r="B8" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>127098449</v>
       </c>
       <c r="B9" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>127096776</v>
       </c>
       <c r="B10" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>127099425</v>
       </c>
       <c r="B11" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2167,32 +2167,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127172695</v>
+        <v>127172679</v>
       </c>
       <c r="B14" t="n">
-        <v>98442</v>
+        <v>96696</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529980</v>
+        <v>530000</v>
       </c>
       <c r="R14" t="n">
-        <v>6999916</v>
+        <v>6999721</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2264,32 +2264,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127172679</v>
+        <v>127172695</v>
       </c>
       <c r="B15" t="n">
-        <v>96695</v>
+        <v>98443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>530000</v>
+        <v>529980</v>
       </c>
       <c r="R15" t="n">
-        <v>6999721</v>
+        <v>6999916</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2461,7 +2461,7 @@
         <v>127172682</v>
       </c>
       <c r="B17" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127172700</v>
+        <v>127172698</v>
       </c>
       <c r="B20" t="n">
         <v>79014</v>
@@ -2797,10 +2797,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>530029</v>
+        <v>529927</v>
       </c>
       <c r="R20" t="n">
-        <v>6999789</v>
+        <v>6999903</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2859,7 +2859,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127172698</v>
+        <v>127172700</v>
       </c>
       <c r="B21" t="n">
         <v>79014</v>
@@ -2894,10 +2894,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529927</v>
+        <v>530029</v>
       </c>
       <c r="R21" t="n">
-        <v>6999903</v>
+        <v>6999789</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3053,32 +3053,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127172696</v>
+        <v>127172678</v>
       </c>
       <c r="B23" t="n">
-        <v>98442</v>
+        <v>75138</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>530028</v>
+        <v>529804</v>
       </c>
       <c r="R23" t="n">
-        <v>6999912</v>
+        <v>6999861</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3150,32 +3150,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127172678</v>
+        <v>127172696</v>
       </c>
       <c r="B24" t="n">
-        <v>75138</v>
+        <v>98443</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529804</v>
+        <v>530028</v>
       </c>
       <c r="R24" t="n">
-        <v>6999861</v>
+        <v>6999912</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3247,45 +3247,53 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127172697</v>
+        <v>127172684</v>
       </c>
       <c r="B25" t="n">
-        <v>98442</v>
+        <v>57657</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Södra Rörmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>530041</v>
+        <v>530054</v>
       </c>
       <c r="R25" t="n">
-        <v>6999921</v>
+        <v>6999817</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3318,6 +3326,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3344,53 +3357,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127172684</v>
+        <v>127172697</v>
       </c>
       <c r="B26" t="n">
-        <v>57657</v>
+        <v>98443</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Södra Rörmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>530054</v>
+        <v>530041</v>
       </c>
       <c r="R26" t="n">
-        <v>6999817</v>
+        <v>6999921</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3423,11 +3428,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3748,7 +3748,7 @@
         <v>127172680</v>
       </c>
       <c r="B30" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>127172681</v>
       </c>
       <c r="B33" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 32741-2025 artfynd.xlsx
+++ b/artfynd/A 32741-2025 artfynd.xlsx
@@ -3357,32 +3357,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127172697</v>
+        <v>127172687</v>
       </c>
       <c r="B26" t="n">
-        <v>98443</v>
+        <v>57817</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>530041</v>
+        <v>530040</v>
       </c>
       <c r="R26" t="n">
-        <v>6999921</v>
+        <v>6999850</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3454,32 +3454,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127172687</v>
+        <v>127172697</v>
       </c>
       <c r="B27" t="n">
-        <v>57817</v>
+        <v>98443</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>530040</v>
+        <v>530041</v>
       </c>
       <c r="R27" t="n">
-        <v>6999850</v>
+        <v>6999921</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 32741-2025 artfynd.xlsx
+++ b/artfynd/A 32741-2025 artfynd.xlsx
@@ -2762,7 +2762,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127172698</v>
+        <v>127172700</v>
       </c>
       <c r="B20" t="n">
         <v>79014</v>
@@ -2797,10 +2797,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529927</v>
+        <v>530029</v>
       </c>
       <c r="R20" t="n">
-        <v>6999903</v>
+        <v>6999789</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2859,7 +2859,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127172700</v>
+        <v>127172698</v>
       </c>
       <c r="B21" t="n">
         <v>79014</v>
@@ -2894,10 +2894,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>530029</v>
+        <v>529927</v>
       </c>
       <c r="R21" t="n">
-        <v>6999789</v>
+        <v>6999903</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3247,53 +3247,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127172684</v>
+        <v>127172697</v>
       </c>
       <c r="B25" t="n">
-        <v>57657</v>
+        <v>98443</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Södra Rörmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>530054</v>
+        <v>530041</v>
       </c>
       <c r="R25" t="n">
-        <v>6999817</v>
+        <v>6999921</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3326,11 +3318,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3454,45 +3441,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127172697</v>
+        <v>127172684</v>
       </c>
       <c r="B27" t="n">
-        <v>98443</v>
+        <v>57657</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Södra Rörmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>530041</v>
+        <v>530054</v>
       </c>
       <c r="R27" t="n">
-        <v>6999921</v>
+        <v>6999817</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3525,6 +3520,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3648,10 +3648,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127172693</v>
+        <v>127172680</v>
       </c>
       <c r="B29" t="n">
-        <v>78772</v>
+        <v>91326</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3659,21 +3659,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3683,10 +3683,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529977</v>
+        <v>529987</v>
       </c>
       <c r="R29" t="n">
-        <v>6999869</v>
+        <v>6999807</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3745,10 +3745,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127172680</v>
+        <v>127172693</v>
       </c>
       <c r="B30" t="n">
-        <v>91326</v>
+        <v>78772</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3756,21 +3756,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529987</v>
+        <v>529977</v>
       </c>
       <c r="R30" t="n">
-        <v>6999807</v>
+        <v>6999869</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3939,10 +3939,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127172699</v>
+        <v>127172681</v>
       </c>
       <c r="B32" t="n">
-        <v>79014</v>
+        <v>91326</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3950,21 +3950,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3974,10 +3974,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>530016</v>
+        <v>529827</v>
       </c>
       <c r="R32" t="n">
-        <v>6999865</v>
+        <v>6999866</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4036,10 +4036,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127172681</v>
+        <v>127172699</v>
       </c>
       <c r="B33" t="n">
-        <v>91326</v>
+        <v>79014</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4047,21 +4047,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4071,10 +4071,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529827</v>
+        <v>530016</v>
       </c>
       <c r="R33" t="n">
-        <v>6999866</v>
+        <v>6999865</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 32741-2025 artfynd.xlsx
+++ b/artfynd/A 32741-2025 artfynd.xlsx
@@ -3247,32 +3247,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127172697</v>
+        <v>127172687</v>
       </c>
       <c r="B25" t="n">
-        <v>98443</v>
+        <v>57817</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3282,10 +3282,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>530041</v>
+        <v>530040</v>
       </c>
       <c r="R25" t="n">
-        <v>6999921</v>
+        <v>6999850</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3344,10 +3344,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127172687</v>
+        <v>127172684</v>
       </c>
       <c r="B26" t="n">
-        <v>57817</v>
+        <v>57657</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3355,34 +3355,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Södra Rörmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>530040</v>
+        <v>530054</v>
       </c>
       <c r="R26" t="n">
-        <v>6999850</v>
+        <v>6999817</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3415,6 +3423,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3441,53 +3454,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127172684</v>
+        <v>127172697</v>
       </c>
       <c r="B27" t="n">
-        <v>57657</v>
+        <v>98443</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Södra Rörmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>530054</v>
+        <v>530041</v>
       </c>
       <c r="R27" t="n">
-        <v>6999817</v>
+        <v>6999921</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3520,11 +3525,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 32741-2025 artfynd.xlsx
+++ b/artfynd/A 32741-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127098716</v>
+        <v>127096398</v>
       </c>
       <c r="B2" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529925</v>
+        <v>529736</v>
       </c>
       <c r="R2" t="n">
-        <v>6999898</v>
+        <v>6999860</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,24 +743,9 @@
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -812,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127096398</v>
+        <v>127098716</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -847,13 +832,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529736</v>
+        <v>529925</v>
       </c>
       <c r="R3" t="n">
-        <v>6999860</v>
+        <v>6999898</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,9 +865,24 @@
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -937,7 +937,7 @@
         <v>127098060</v>
       </c>
       <c r="B4" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>127098468</v>
       </c>
       <c r="B5" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>127099015</v>
       </c>
       <c r="B6" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>127098756</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>127097774</v>
       </c>
       <c r="B8" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>127098449</v>
       </c>
       <c r="B9" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>127096776</v>
       </c>
       <c r="B10" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>127099425</v>
       </c>
       <c r="B11" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>127172688</v>
       </c>
       <c r="B12" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>127172686</v>
       </c>
       <c r="B13" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>127172679</v>
       </c>
       <c r="B14" t="n">
-        <v>96696</v>
+        <v>96700</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>127172695</v>
       </c>
       <c r="B15" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>127172694</v>
       </c>
       <c r="B16" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>127172682</v>
       </c>
       <c r="B17" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>127172685</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>127172691</v>
       </c>
       <c r="B19" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>127172700</v>
       </c>
       <c r="B20" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>127172698</v>
       </c>
       <c r="B21" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>127172689</v>
       </c>
       <c r="B22" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         <v>127172678</v>
       </c>
       <c r="B23" t="n">
-        <v>75138</v>
+        <v>75142</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>127172696</v>
       </c>
       <c r="B24" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3247,10 +3247,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127172687</v>
+        <v>127172684</v>
       </c>
       <c r="B25" t="n">
-        <v>57817</v>
+        <v>57661</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3258,34 +3258,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Södra Rörmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>530040</v>
+        <v>530054</v>
       </c>
       <c r="R25" t="n">
-        <v>6999850</v>
+        <v>6999817</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3318,6 +3326,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3344,10 +3357,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127172684</v>
+        <v>127172687</v>
       </c>
       <c r="B26" t="n">
-        <v>57657</v>
+        <v>57821</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3355,42 +3368,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Södra Rörmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>530054</v>
+        <v>530040</v>
       </c>
       <c r="R26" t="n">
-        <v>6999817</v>
+        <v>6999850</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3423,11 +3428,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3457,7 +3457,7 @@
         <v>127172697</v>
       </c>
       <c r="B27" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>127172692</v>
       </c>
       <c r="B28" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3648,10 +3648,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127172680</v>
+        <v>127172693</v>
       </c>
       <c r="B29" t="n">
-        <v>91326</v>
+        <v>78776</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3659,21 +3659,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3683,10 +3683,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529987</v>
+        <v>529977</v>
       </c>
       <c r="R29" t="n">
-        <v>6999807</v>
+        <v>6999869</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3745,10 +3745,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127172693</v>
+        <v>127172680</v>
       </c>
       <c r="B30" t="n">
-        <v>78772</v>
+        <v>91330</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3756,21 +3756,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529977</v>
+        <v>529987</v>
       </c>
       <c r="R30" t="n">
-        <v>6999869</v>
+        <v>6999807</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3845,7 +3845,7 @@
         <v>127172701</v>
       </c>
       <c r="B31" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>127172681</v>
       </c>
       <c r="B32" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>127172699</v>
       </c>
       <c r="B33" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 32741-2025 artfynd.xlsx
+++ b/artfynd/A 32741-2025 artfynd.xlsx
@@ -675,48 +675,58 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127096398</v>
+        <v>127098060</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>98468</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529736</v>
+        <v>529843</v>
       </c>
       <c r="R2" t="n">
-        <v>6999860</v>
+        <v>6999863</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,11 +753,21 @@
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -760,26 +780,6 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -934,58 +934,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127098060</v>
+        <v>127096398</v>
       </c>
       <c r="B4" t="n">
-        <v>98468</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529843</v>
+        <v>529736</v>
       </c>
       <c r="R4" t="n">
-        <v>6999863</v>
+        <v>6999860</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,21 +1002,11 @@
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1039,6 +1019,26 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -2167,32 +2167,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127172679</v>
+        <v>127172695</v>
       </c>
       <c r="B14" t="n">
-        <v>96700</v>
+        <v>98447</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>530000</v>
+        <v>529980</v>
       </c>
       <c r="R14" t="n">
-        <v>6999721</v>
+        <v>6999916</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2264,32 +2264,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127172695</v>
+        <v>127172679</v>
       </c>
       <c r="B15" t="n">
-        <v>98447</v>
+        <v>96700</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529980</v>
+        <v>530000</v>
       </c>
       <c r="R15" t="n">
-        <v>6999916</v>
+        <v>6999721</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 32741-2025 artfynd.xlsx
+++ b/artfynd/A 32741-2025 artfynd.xlsx
@@ -3247,53 +3247,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127172684</v>
+        <v>127172697</v>
       </c>
       <c r="B25" t="n">
-        <v>57661</v>
+        <v>98447</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Södra Rörmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>530054</v>
+        <v>530041</v>
       </c>
       <c r="R25" t="n">
-        <v>6999817</v>
+        <v>6999921</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3326,11 +3318,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3357,10 +3344,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127172687</v>
+        <v>127172684</v>
       </c>
       <c r="B26" t="n">
-        <v>57821</v>
+        <v>57661</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3368,34 +3355,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Södra Rörmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>530040</v>
+        <v>530054</v>
       </c>
       <c r="R26" t="n">
-        <v>6999850</v>
+        <v>6999817</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3428,6 +3423,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3454,32 +3454,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127172697</v>
+        <v>127172687</v>
       </c>
       <c r="B27" t="n">
-        <v>98447</v>
+        <v>57821</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>530041</v>
+        <v>530040</v>
       </c>
       <c r="R27" t="n">
-        <v>6999921</v>
+        <v>6999850</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3648,10 +3648,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127172693</v>
+        <v>127172680</v>
       </c>
       <c r="B29" t="n">
-        <v>78776</v>
+        <v>91330</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3659,21 +3659,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3683,10 +3683,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529977</v>
+        <v>529987</v>
       </c>
       <c r="R29" t="n">
-        <v>6999869</v>
+        <v>6999807</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3745,10 +3745,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127172680</v>
+        <v>127172693</v>
       </c>
       <c r="B30" t="n">
-        <v>91330</v>
+        <v>78776</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3756,21 +3756,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529987</v>
+        <v>529977</v>
       </c>
       <c r="R30" t="n">
-        <v>6999807</v>
+        <v>6999869</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 32741-2025 artfynd.xlsx
+++ b/artfynd/A 32741-2025 artfynd.xlsx
@@ -675,55 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127098060</v>
+        <v>127098716</v>
       </c>
       <c r="B2" t="n">
-        <v>98468</v>
+        <v>79018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529843</v>
+        <v>529925</v>
       </c>
       <c r="R2" t="n">
-        <v>6999863</v>
+        <v>6999898</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
@@ -755,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,6 +775,26 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,7 +812,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127098716</v>
+        <v>127096398</v>
       </c>
       <c r="B3" t="n">
         <v>79018</v>
@@ -832,13 +847,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529925</v>
+        <v>529736</v>
       </c>
       <c r="R3" t="n">
-        <v>6999898</v>
+        <v>6999860</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,24 +880,9 @@
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,48 +934,58 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127096398</v>
+        <v>127098060</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>98468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529736</v>
+        <v>529843</v>
       </c>
       <c r="R4" t="n">
-        <v>6999860</v>
+        <v>6999863</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1002,11 +1012,21 @@
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1019,26 +1039,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -3247,45 +3247,53 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127172697</v>
+        <v>127172684</v>
       </c>
       <c r="B25" t="n">
-        <v>98447</v>
+        <v>57661</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Södra Rörmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>530041</v>
+        <v>530054</v>
       </c>
       <c r="R25" t="n">
-        <v>6999921</v>
+        <v>6999817</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3318,6 +3326,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3344,10 +3357,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127172684</v>
+        <v>127172687</v>
       </c>
       <c r="B26" t="n">
-        <v>57661</v>
+        <v>57821</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3355,42 +3368,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Södra Rörmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>530054</v>
+        <v>530040</v>
       </c>
       <c r="R26" t="n">
-        <v>6999817</v>
+        <v>6999850</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3423,11 +3428,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3454,32 +3454,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127172687</v>
+        <v>127172697</v>
       </c>
       <c r="B27" t="n">
-        <v>57821</v>
+        <v>98447</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>530040</v>
+        <v>530041</v>
       </c>
       <c r="R27" t="n">
-        <v>6999850</v>
+        <v>6999921</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3648,10 +3648,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127172680</v>
+        <v>127172693</v>
       </c>
       <c r="B29" t="n">
-        <v>91330</v>
+        <v>78776</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3659,21 +3659,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3683,10 +3683,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529987</v>
+        <v>529977</v>
       </c>
       <c r="R29" t="n">
-        <v>6999807</v>
+        <v>6999869</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3745,10 +3745,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127172693</v>
+        <v>127172680</v>
       </c>
       <c r="B30" t="n">
-        <v>78776</v>
+        <v>91330</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3756,21 +3756,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529977</v>
+        <v>529987</v>
       </c>
       <c r="R30" t="n">
-        <v>6999869</v>
+        <v>6999807</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 32741-2025 artfynd.xlsx
+++ b/artfynd/A 32741-2025 artfynd.xlsx
@@ -937,7 +937,7 @@
         <v>127098060</v>
       </c>
       <c r="B4" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>127099015</v>
       </c>
       <c r="B6" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>127097774</v>
       </c>
       <c r="B8" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>127098449</v>
       </c>
       <c r="B9" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>127096776</v>
       </c>
       <c r="B10" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>127099425</v>
       </c>
       <c r="B11" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2167,32 +2167,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127172695</v>
+        <v>127172679</v>
       </c>
       <c r="B14" t="n">
-        <v>98447</v>
+        <v>96700</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529980</v>
+        <v>530000</v>
       </c>
       <c r="R14" t="n">
-        <v>6999916</v>
+        <v>6999721</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2264,32 +2264,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127172679</v>
+        <v>127172695</v>
       </c>
       <c r="B15" t="n">
-        <v>96700</v>
+        <v>98448</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>530000</v>
+        <v>529980</v>
       </c>
       <c r="R15" t="n">
-        <v>6999721</v>
+        <v>6999916</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -3153,7 +3153,7 @@
         <v>127172696</v>
       </c>
       <c r="B24" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3247,10 +3247,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127172684</v>
+        <v>127172687</v>
       </c>
       <c r="B25" t="n">
-        <v>57661</v>
+        <v>57821</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3258,42 +3258,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Södra Rörmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>530054</v>
+        <v>530040</v>
       </c>
       <c r="R25" t="n">
-        <v>6999817</v>
+        <v>6999850</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3326,11 +3318,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3357,10 +3344,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127172687</v>
+        <v>127172684</v>
       </c>
       <c r="B26" t="n">
-        <v>57821</v>
+        <v>57661</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3368,34 +3355,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Södra Rörmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>530040</v>
+        <v>530054</v>
       </c>
       <c r="R26" t="n">
-        <v>6999850</v>
+        <v>6999817</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3428,6 +3423,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3457,7 +3457,7 @@
         <v>127172697</v>
       </c>
       <c r="B27" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3648,10 +3648,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127172693</v>
+        <v>127172680</v>
       </c>
       <c r="B29" t="n">
-        <v>78776</v>
+        <v>91330</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3659,21 +3659,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3683,10 +3683,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529977</v>
+        <v>529987</v>
       </c>
       <c r="R29" t="n">
-        <v>6999869</v>
+        <v>6999807</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3745,10 +3745,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127172680</v>
+        <v>127172693</v>
       </c>
       <c r="B30" t="n">
-        <v>91330</v>
+        <v>78776</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3756,21 +3756,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529987</v>
+        <v>529977</v>
       </c>
       <c r="R30" t="n">
-        <v>6999807</v>
+        <v>6999869</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 32741-2025 artfynd.xlsx
+++ b/artfynd/A 32741-2025 artfynd.xlsx
@@ -3053,32 +3053,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127172678</v>
+        <v>127172696</v>
       </c>
       <c r="B23" t="n">
-        <v>75142</v>
+        <v>98448</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>529804</v>
+        <v>530028</v>
       </c>
       <c r="R23" t="n">
-        <v>6999861</v>
+        <v>6999912</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3150,32 +3150,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127172696</v>
+        <v>127172678</v>
       </c>
       <c r="B24" t="n">
-        <v>98448</v>
+        <v>75142</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>530028</v>
+        <v>529804</v>
       </c>
       <c r="R24" t="n">
-        <v>6999912</v>
+        <v>6999861</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 32741-2025 artfynd.xlsx
+++ b/artfynd/A 32741-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127098716</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         <v>127096398</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>127098060</v>
       </c>
       <c r="B4" t="n">
-        <v>98469</v>
+        <v>98471</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>127098468</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>127099015</v>
       </c>
       <c r="B6" t="n">
-        <v>98469</v>
+        <v>98471</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>127098756</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>127097774</v>
       </c>
       <c r="B8" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>127098449</v>
       </c>
       <c r="B9" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>127096776</v>
       </c>
       <c r="B10" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>127099425</v>
       </c>
       <c r="B11" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>127172688</v>
       </c>
       <c r="B12" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>127172686</v>
       </c>
       <c r="B13" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>127172679</v>
       </c>
       <c r="B14" t="n">
-        <v>96700</v>
+        <v>96702</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>127172695</v>
       </c>
       <c r="B15" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>127172694</v>
       </c>
       <c r="B16" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>127172682</v>
       </c>
       <c r="B17" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>127172685</v>
       </c>
       <c r="B18" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>127172691</v>
       </c>
       <c r="B19" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2762,10 +2762,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127172700</v>
+        <v>127172698</v>
       </c>
       <c r="B20" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2797,10 +2797,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>530029</v>
+        <v>529927</v>
       </c>
       <c r="R20" t="n">
-        <v>6999789</v>
+        <v>6999903</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2859,10 +2859,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127172698</v>
+        <v>127172689</v>
       </c>
       <c r="B21" t="n">
-        <v>79018</v>
+        <v>57823</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2870,21 +2870,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2894,10 +2894,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529927</v>
+        <v>529921</v>
       </c>
       <c r="R21" t="n">
-        <v>6999903</v>
+        <v>6999851</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2956,10 +2956,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127172689</v>
+        <v>127172700</v>
       </c>
       <c r="B22" t="n">
-        <v>57821</v>
+        <v>79020</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2967,21 +2967,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529921</v>
+        <v>530029</v>
       </c>
       <c r="R22" t="n">
-        <v>6999851</v>
+        <v>6999789</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3053,32 +3053,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127172696</v>
+        <v>127172678</v>
       </c>
       <c r="B23" t="n">
-        <v>98448</v>
+        <v>75144</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>530028</v>
+        <v>529804</v>
       </c>
       <c r="R23" t="n">
-        <v>6999912</v>
+        <v>6999861</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3150,32 +3150,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127172678</v>
+        <v>127172696</v>
       </c>
       <c r="B24" t="n">
-        <v>75142</v>
+        <v>98450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529804</v>
+        <v>530028</v>
       </c>
       <c r="R24" t="n">
-        <v>6999861</v>
+        <v>6999912</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3247,10 +3247,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127172687</v>
+        <v>127172684</v>
       </c>
       <c r="B25" t="n">
-        <v>57821</v>
+        <v>57663</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3258,34 +3258,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Södra Rörmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>530040</v>
+        <v>530054</v>
       </c>
       <c r="R25" t="n">
-        <v>6999850</v>
+        <v>6999817</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3318,6 +3326,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3344,53 +3357,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127172684</v>
+        <v>127172697</v>
       </c>
       <c r="B26" t="n">
-        <v>57661</v>
+        <v>98450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Södra Rörmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>530054</v>
+        <v>530041</v>
       </c>
       <c r="R26" t="n">
-        <v>6999817</v>
+        <v>6999921</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3423,11 +3428,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3454,32 +3454,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127172697</v>
+        <v>127172687</v>
       </c>
       <c r="B27" t="n">
-        <v>98448</v>
+        <v>57823</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>530041</v>
+        <v>530040</v>
       </c>
       <c r="R27" t="n">
-        <v>6999921</v>
+        <v>6999850</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3554,7 +3554,7 @@
         <v>127172692</v>
       </c>
       <c r="B28" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>127172680</v>
       </c>
       <c r="B29" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>127172693</v>
       </c>
       <c r="B30" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>127172701</v>
       </c>
       <c r="B31" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3939,10 +3939,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127172681</v>
+        <v>127172699</v>
       </c>
       <c r="B32" t="n">
-        <v>91330</v>
+        <v>79020</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3950,21 +3950,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3974,10 +3974,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>529827</v>
+        <v>530016</v>
       </c>
       <c r="R32" t="n">
-        <v>6999866</v>
+        <v>6999865</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4036,10 +4036,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127172699</v>
+        <v>127172681</v>
       </c>
       <c r="B33" t="n">
-        <v>79018</v>
+        <v>91332</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4047,21 +4047,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4071,10 +4071,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>530016</v>
+        <v>529827</v>
       </c>
       <c r="R33" t="n">
-        <v>6999865</v>
+        <v>6999866</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 32741-2025 artfynd.xlsx
+++ b/artfynd/A 32741-2025 artfynd.xlsx
@@ -2762,7 +2762,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127172698</v>
+        <v>127172700</v>
       </c>
       <c r="B20" t="n">
         <v>79020</v>
@@ -2797,10 +2797,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529927</v>
+        <v>530029</v>
       </c>
       <c r="R20" t="n">
-        <v>6999903</v>
+        <v>6999789</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2859,10 +2859,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127172689</v>
+        <v>127172698</v>
       </c>
       <c r="B21" t="n">
-        <v>57823</v>
+        <v>79020</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2870,21 +2870,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2894,10 +2894,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529921</v>
+        <v>529927</v>
       </c>
       <c r="R21" t="n">
-        <v>6999851</v>
+        <v>6999903</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2956,10 +2956,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127172700</v>
+        <v>127172689</v>
       </c>
       <c r="B22" t="n">
-        <v>79020</v>
+        <v>57823</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2967,21 +2967,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>530029</v>
+        <v>529921</v>
       </c>
       <c r="R22" t="n">
-        <v>6999789</v>
+        <v>6999851</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3247,53 +3247,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127172684</v>
+        <v>127172697</v>
       </c>
       <c r="B25" t="n">
-        <v>57663</v>
+        <v>98450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Södra Rörmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>530054</v>
+        <v>530041</v>
       </c>
       <c r="R25" t="n">
-        <v>6999817</v>
+        <v>6999921</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3326,11 +3318,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3357,45 +3344,53 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127172697</v>
+        <v>127172684</v>
       </c>
       <c r="B26" t="n">
-        <v>98450</v>
+        <v>57663</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Södra Rörmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>530041</v>
+        <v>530054</v>
       </c>
       <c r="R26" t="n">
-        <v>6999921</v>
+        <v>6999817</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3428,6 +3423,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3648,10 +3648,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127172680</v>
+        <v>127172693</v>
       </c>
       <c r="B29" t="n">
-        <v>91332</v>
+        <v>78778</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3659,21 +3659,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3683,10 +3683,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529987</v>
+        <v>529977</v>
       </c>
       <c r="R29" t="n">
-        <v>6999807</v>
+        <v>6999869</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3745,10 +3745,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127172693</v>
+        <v>127172680</v>
       </c>
       <c r="B30" t="n">
-        <v>78778</v>
+        <v>91332</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3756,21 +3756,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529977</v>
+        <v>529987</v>
       </c>
       <c r="R30" t="n">
-        <v>6999869</v>
+        <v>6999807</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 32741-2025 artfynd.xlsx
+++ b/artfynd/A 32741-2025 artfynd.xlsx
@@ -812,48 +812,58 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127096398</v>
+        <v>127098060</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>98471</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529736</v>
+        <v>529843</v>
       </c>
       <c r="R3" t="n">
-        <v>6999860</v>
+        <v>6999863</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,11 +890,21 @@
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -897,26 +917,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -934,58 +934,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127098060</v>
+        <v>127096398</v>
       </c>
       <c r="B4" t="n">
-        <v>98471</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529843</v>
+        <v>529736</v>
       </c>
       <c r="R4" t="n">
-        <v>6999863</v>
+        <v>6999860</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,21 +1002,11 @@
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1039,6 +1019,26 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -3053,32 +3053,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127172678</v>
+        <v>127172696</v>
       </c>
       <c r="B23" t="n">
-        <v>75144</v>
+        <v>98450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>529804</v>
+        <v>530028</v>
       </c>
       <c r="R23" t="n">
-        <v>6999861</v>
+        <v>6999912</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3150,32 +3150,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127172696</v>
+        <v>127172678</v>
       </c>
       <c r="B24" t="n">
-        <v>98450</v>
+        <v>75144</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>530028</v>
+        <v>529804</v>
       </c>
       <c r="R24" t="n">
-        <v>6999912</v>
+        <v>6999861</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3247,45 +3247,53 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127172697</v>
+        <v>127172684</v>
       </c>
       <c r="B25" t="n">
-        <v>98450</v>
+        <v>57663</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Södra Rörmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>530041</v>
+        <v>530054</v>
       </c>
       <c r="R25" t="n">
-        <v>6999921</v>
+        <v>6999817</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3318,6 +3326,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3344,10 +3357,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127172684</v>
+        <v>127172687</v>
       </c>
       <c r="B26" t="n">
-        <v>57663</v>
+        <v>57823</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3355,42 +3368,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Södra Rörmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>530054</v>
+        <v>530040</v>
       </c>
       <c r="R26" t="n">
-        <v>6999817</v>
+        <v>6999850</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3423,11 +3428,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3454,32 +3454,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127172687</v>
+        <v>127172697</v>
       </c>
       <c r="B27" t="n">
-        <v>57823</v>
+        <v>98450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>530040</v>
+        <v>530041</v>
       </c>
       <c r="R27" t="n">
-        <v>6999850</v>
+        <v>6999921</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 32741-2025 artfynd.xlsx
+++ b/artfynd/A 32741-2025 artfynd.xlsx
@@ -812,58 +812,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127098060</v>
+        <v>127096398</v>
       </c>
       <c r="B3" t="n">
-        <v>98471</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529843</v>
+        <v>529736</v>
       </c>
       <c r="R3" t="n">
-        <v>6999863</v>
+        <v>6999860</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -890,21 +880,11 @@
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -917,6 +897,26 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -934,48 +934,58 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127096398</v>
+        <v>127098060</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>98477</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529736</v>
+        <v>529843</v>
       </c>
       <c r="R4" t="n">
-        <v>6999860</v>
+        <v>6999863</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1002,11 +1012,21 @@
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1019,26 +1039,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1181,7 +1181,7 @@
         <v>127099015</v>
       </c>
       <c r="B6" t="n">
-        <v>98471</v>
+        <v>98477</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>127097774</v>
       </c>
       <c r="B8" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>127098449</v>
       </c>
       <c r="B9" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>127096776</v>
       </c>
       <c r="B10" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>127099425</v>
       </c>
       <c r="B11" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2167,32 +2167,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127172679</v>
+        <v>127172695</v>
       </c>
       <c r="B14" t="n">
-        <v>96702</v>
+        <v>98456</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>530000</v>
+        <v>529980</v>
       </c>
       <c r="R14" t="n">
-        <v>6999721</v>
+        <v>6999916</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2264,32 +2264,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127172695</v>
+        <v>127172679</v>
       </c>
       <c r="B15" t="n">
-        <v>98450</v>
+        <v>96708</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529980</v>
+        <v>530000</v>
       </c>
       <c r="R15" t="n">
-        <v>6999916</v>
+        <v>6999721</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2461,7 +2461,7 @@
         <v>127172682</v>
       </c>
       <c r="B17" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127172700</v>
+        <v>127172698</v>
       </c>
       <c r="B20" t="n">
         <v>79020</v>
@@ -2797,10 +2797,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>530029</v>
+        <v>529927</v>
       </c>
       <c r="R20" t="n">
-        <v>6999789</v>
+        <v>6999903</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2859,7 +2859,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127172698</v>
+        <v>127172700</v>
       </c>
       <c r="B21" t="n">
         <v>79020</v>
@@ -2894,10 +2894,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529927</v>
+        <v>530029</v>
       </c>
       <c r="R21" t="n">
-        <v>6999903</v>
+        <v>6999789</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3056,7 +3056,7 @@
         <v>127172696</v>
       </c>
       <c r="B23" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3357,32 +3357,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127172687</v>
+        <v>127172697</v>
       </c>
       <c r="B26" t="n">
-        <v>57823</v>
+        <v>98456</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>530040</v>
+        <v>530041</v>
       </c>
       <c r="R26" t="n">
-        <v>6999850</v>
+        <v>6999921</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3454,32 +3454,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127172697</v>
+        <v>127172687</v>
       </c>
       <c r="B27" t="n">
-        <v>98450</v>
+        <v>57823</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>530041</v>
+        <v>530040</v>
       </c>
       <c r="R27" t="n">
-        <v>6999921</v>
+        <v>6999850</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3748,7 +3748,7 @@
         <v>127172680</v>
       </c>
       <c r="B30" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>127172681</v>
       </c>
       <c r="B33" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 32741-2025 artfynd.xlsx
+++ b/artfynd/A 32741-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127098716</v>
+        <v>127096398</v>
       </c>
       <c r="B2" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529925</v>
+        <v>529736</v>
       </c>
       <c r="R2" t="n">
-        <v>6999898</v>
+        <v>6999860</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,24 +743,9 @@
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -812,48 +797,58 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127096398</v>
+        <v>127098060</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>98480</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529736</v>
+        <v>529843</v>
       </c>
       <c r="R3" t="n">
-        <v>6999860</v>
+        <v>6999863</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,11 +875,21 @@
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -897,26 +902,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -934,55 +919,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127098060</v>
+        <v>127098716</v>
       </c>
       <c r="B4" t="n">
-        <v>98477</v>
+        <v>79023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529843</v>
+        <v>529925</v>
       </c>
       <c r="R4" t="n">
-        <v>6999863</v>
+        <v>6999898</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -1014,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1024,7 +999,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,6 +1019,26 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1059,7 +1059,7 @@
         <v>127098468</v>
       </c>
       <c r="B5" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>127099015</v>
       </c>
       <c r="B6" t="n">
-        <v>98477</v>
+        <v>98480</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>127098756</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>127097774</v>
       </c>
       <c r="B8" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>127098449</v>
       </c>
       <c r="B9" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>127096776</v>
       </c>
       <c r="B10" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>127099425</v>
       </c>
       <c r="B11" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>127172688</v>
       </c>
       <c r="B12" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>127172686</v>
       </c>
       <c r="B13" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2167,32 +2167,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127172695</v>
+        <v>127172679</v>
       </c>
       <c r="B14" t="n">
-        <v>98456</v>
+        <v>96711</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529980</v>
+        <v>530000</v>
       </c>
       <c r="R14" t="n">
-        <v>6999916</v>
+        <v>6999721</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2264,32 +2264,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127172679</v>
+        <v>127172695</v>
       </c>
       <c r="B15" t="n">
-        <v>96708</v>
+        <v>98459</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>530000</v>
+        <v>529980</v>
       </c>
       <c r="R15" t="n">
-        <v>6999721</v>
+        <v>6999916</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2364,7 +2364,7 @@
         <v>127172694</v>
       </c>
       <c r="B16" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>127172682</v>
       </c>
       <c r="B17" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>127172685</v>
       </c>
       <c r="B18" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>127172691</v>
       </c>
       <c r="B19" t="n">
-        <v>80152</v>
+        <v>80155</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2762,10 +2762,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127172698</v>
+        <v>127172689</v>
       </c>
       <c r="B20" t="n">
-        <v>79020</v>
+        <v>57826</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2773,21 +2773,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2797,10 +2797,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529927</v>
+        <v>529921</v>
       </c>
       <c r="R20" t="n">
-        <v>6999903</v>
+        <v>6999851</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2862,7 +2862,7 @@
         <v>127172700</v>
       </c>
       <c r="B21" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2956,10 +2956,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127172689</v>
+        <v>127172698</v>
       </c>
       <c r="B22" t="n">
-        <v>57823</v>
+        <v>79023</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2967,21 +2967,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529921</v>
+        <v>529927</v>
       </c>
       <c r="R22" t="n">
-        <v>6999851</v>
+        <v>6999903</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3053,32 +3053,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127172696</v>
+        <v>127172678</v>
       </c>
       <c r="B23" t="n">
-        <v>98456</v>
+        <v>75147</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>530028</v>
+        <v>529804</v>
       </c>
       <c r="R23" t="n">
-        <v>6999912</v>
+        <v>6999861</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3150,32 +3150,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127172678</v>
+        <v>127172696</v>
       </c>
       <c r="B24" t="n">
-        <v>75144</v>
+        <v>98459</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529804</v>
+        <v>530028</v>
       </c>
       <c r="R24" t="n">
-        <v>6999861</v>
+        <v>6999912</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3250,7 +3250,7 @@
         <v>127172684</v>
       </c>
       <c r="B25" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3357,32 +3357,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127172697</v>
+        <v>127172687</v>
       </c>
       <c r="B26" t="n">
-        <v>98456</v>
+        <v>57826</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>530041</v>
+        <v>530040</v>
       </c>
       <c r="R26" t="n">
-        <v>6999921</v>
+        <v>6999850</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3454,32 +3454,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127172687</v>
+        <v>127172697</v>
       </c>
       <c r="B27" t="n">
-        <v>57823</v>
+        <v>98459</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>530040</v>
+        <v>530041</v>
       </c>
       <c r="R27" t="n">
-        <v>6999850</v>
+        <v>6999921</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3554,7 +3554,7 @@
         <v>127172692</v>
       </c>
       <c r="B28" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3648,10 +3648,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127172693</v>
+        <v>127172680</v>
       </c>
       <c r="B29" t="n">
-        <v>78778</v>
+        <v>91341</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3659,21 +3659,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3683,10 +3683,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529977</v>
+        <v>529987</v>
       </c>
       <c r="R29" t="n">
-        <v>6999869</v>
+        <v>6999807</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3745,10 +3745,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127172680</v>
+        <v>127172693</v>
       </c>
       <c r="B30" t="n">
-        <v>91338</v>
+        <v>78781</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3756,21 +3756,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529987</v>
+        <v>529977</v>
       </c>
       <c r="R30" t="n">
-        <v>6999807</v>
+        <v>6999869</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3845,7 +3845,7 @@
         <v>127172701</v>
       </c>
       <c r="B31" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3939,10 +3939,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127172699</v>
+        <v>127172681</v>
       </c>
       <c r="B32" t="n">
-        <v>79020</v>
+        <v>91341</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3950,21 +3950,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3974,10 +3974,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>530016</v>
+        <v>529827</v>
       </c>
       <c r="R32" t="n">
-        <v>6999865</v>
+        <v>6999866</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4036,10 +4036,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127172681</v>
+        <v>127172699</v>
       </c>
       <c r="B33" t="n">
-        <v>91338</v>
+        <v>79023</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4047,21 +4047,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4071,10 +4071,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529827</v>
+        <v>530016</v>
       </c>
       <c r="R33" t="n">
-        <v>6999866</v>
+        <v>6999865</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 32741-2025 artfynd.xlsx
+++ b/artfynd/A 32741-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127096398</v>
       </c>
       <c r="B2" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,55 +797,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127098060</v>
+        <v>127098716</v>
       </c>
       <c r="B3" t="n">
-        <v>98480</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529843</v>
+        <v>529925</v>
       </c>
       <c r="R3" t="n">
-        <v>6999863</v>
+        <v>6999898</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -877,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,6 +897,26 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -919,45 +934,55 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127098716</v>
+        <v>127098060</v>
       </c>
       <c r="B4" t="n">
-        <v>79023</v>
+        <v>98488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529925</v>
+        <v>529843</v>
       </c>
       <c r="R4" t="n">
-        <v>6999898</v>
+        <v>6999863</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -989,7 +1014,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,12 +1024,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,26 +1039,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1059,7 +1059,7 @@
         <v>127098468</v>
       </c>
       <c r="B5" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>127099015</v>
       </c>
       <c r="B6" t="n">
-        <v>98480</v>
+        <v>98488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>127098756</v>
       </c>
       <c r="B7" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>127097774</v>
       </c>
       <c r="B8" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>127098449</v>
       </c>
       <c r="B9" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>127096776</v>
       </c>
       <c r="B10" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>127099425</v>
       </c>
       <c r="B11" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>127172688</v>
       </c>
       <c r="B12" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>127172686</v>
       </c>
       <c r="B13" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>127172679</v>
       </c>
       <c r="B14" t="n">
-        <v>96711</v>
+        <v>96719</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>127172695</v>
       </c>
       <c r="B15" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>127172694</v>
       </c>
       <c r="B16" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>127172682</v>
       </c>
       <c r="B17" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>127172685</v>
       </c>
       <c r="B18" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>127172691</v>
       </c>
       <c r="B19" t="n">
-        <v>80155</v>
+        <v>80161</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>127172689</v>
       </c>
       <c r="B20" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2859,10 +2859,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127172700</v>
+        <v>127172698</v>
       </c>
       <c r="B21" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2894,10 +2894,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>530029</v>
+        <v>529927</v>
       </c>
       <c r="R21" t="n">
-        <v>6999789</v>
+        <v>6999903</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2956,10 +2956,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127172698</v>
+        <v>127172700</v>
       </c>
       <c r="B22" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529927</v>
+        <v>530029</v>
       </c>
       <c r="R22" t="n">
-        <v>6999903</v>
+        <v>6999789</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3053,32 +3053,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127172678</v>
+        <v>127172696</v>
       </c>
       <c r="B23" t="n">
-        <v>75147</v>
+        <v>98467</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>529804</v>
+        <v>530028</v>
       </c>
       <c r="R23" t="n">
-        <v>6999861</v>
+        <v>6999912</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3150,32 +3150,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127172696</v>
+        <v>127172678</v>
       </c>
       <c r="B24" t="n">
-        <v>98459</v>
+        <v>75153</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>530028</v>
+        <v>529804</v>
       </c>
       <c r="R24" t="n">
-        <v>6999912</v>
+        <v>6999861</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3250,7 +3250,7 @@
         <v>127172684</v>
       </c>
       <c r="B25" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>127172687</v>
       </c>
       <c r="B26" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>127172697</v>
       </c>
       <c r="B27" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>127172692</v>
       </c>
       <c r="B28" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>127172680</v>
       </c>
       <c r="B29" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>127172693</v>
       </c>
       <c r="B30" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>127172701</v>
       </c>
       <c r="B31" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>127172681</v>
       </c>
       <c r="B32" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>127172699</v>
       </c>
       <c r="B33" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 32741-2025 artfynd.xlsx
+++ b/artfynd/A 32741-2025 artfynd.xlsx
@@ -2167,32 +2167,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127172679</v>
+        <v>127172695</v>
       </c>
       <c r="B14" t="n">
-        <v>96719</v>
+        <v>98468</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>530000</v>
+        <v>529980</v>
       </c>
       <c r="R14" t="n">
-        <v>6999721</v>
+        <v>6999916</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2264,32 +2264,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127172695</v>
+        <v>127172679</v>
       </c>
       <c r="B15" t="n">
-        <v>98467</v>
+        <v>96720</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529980</v>
+        <v>530000</v>
       </c>
       <c r="R15" t="n">
-        <v>6999916</v>
+        <v>6999721</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2461,7 +2461,7 @@
         <v>127172682</v>
       </c>
       <c r="B17" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127172698</v>
+        <v>127172700</v>
       </c>
       <c r="B21" t="n">
         <v>79029</v>
@@ -2894,10 +2894,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529927</v>
+        <v>530029</v>
       </c>
       <c r="R21" t="n">
-        <v>6999903</v>
+        <v>6999789</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2956,7 +2956,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127172700</v>
+        <v>127172698</v>
       </c>
       <c r="B22" t="n">
         <v>79029</v>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>530029</v>
+        <v>529927</v>
       </c>
       <c r="R22" t="n">
-        <v>6999789</v>
+        <v>6999903</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3053,32 +3053,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127172696</v>
+        <v>127172678</v>
       </c>
       <c r="B23" t="n">
-        <v>98467</v>
+        <v>75153</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>530028</v>
+        <v>529804</v>
       </c>
       <c r="R23" t="n">
-        <v>6999912</v>
+        <v>6999861</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3150,32 +3150,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127172678</v>
+        <v>127172696</v>
       </c>
       <c r="B24" t="n">
-        <v>75153</v>
+        <v>98468</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529804</v>
+        <v>530028</v>
       </c>
       <c r="R24" t="n">
-        <v>6999861</v>
+        <v>6999912</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3247,10 +3247,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127172684</v>
+        <v>127172687</v>
       </c>
       <c r="B25" t="n">
-        <v>57672</v>
+        <v>57832</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3258,42 +3258,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Södra Rörmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>530054</v>
+        <v>530040</v>
       </c>
       <c r="R25" t="n">
-        <v>6999817</v>
+        <v>6999850</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3326,11 +3318,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3357,32 +3344,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127172687</v>
+        <v>127172697</v>
       </c>
       <c r="B26" t="n">
-        <v>57832</v>
+        <v>98468</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3392,10 +3379,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>530040</v>
+        <v>530041</v>
       </c>
       <c r="R26" t="n">
-        <v>6999850</v>
+        <v>6999921</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3454,45 +3441,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127172697</v>
+        <v>127172684</v>
       </c>
       <c r="B27" t="n">
-        <v>98467</v>
+        <v>57672</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Södra Rörmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>530041</v>
+        <v>530054</v>
       </c>
       <c r="R27" t="n">
-        <v>6999921</v>
+        <v>6999817</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3525,6 +3520,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3648,10 +3648,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127172680</v>
+        <v>127172693</v>
       </c>
       <c r="B29" t="n">
-        <v>91349</v>
+        <v>78787</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3659,21 +3659,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3683,10 +3683,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529987</v>
+        <v>529977</v>
       </c>
       <c r="R29" t="n">
-        <v>6999807</v>
+        <v>6999869</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3745,10 +3745,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127172693</v>
+        <v>127172680</v>
       </c>
       <c r="B30" t="n">
-        <v>78787</v>
+        <v>91350</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3756,21 +3756,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529977</v>
+        <v>529987</v>
       </c>
       <c r="R30" t="n">
-        <v>6999869</v>
+        <v>6999807</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3942,7 +3942,7 @@
         <v>127172681</v>
       </c>
       <c r="B32" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 32741-2025 artfynd.xlsx
+++ b/artfynd/A 32741-2025 artfynd.xlsx
@@ -675,48 +675,58 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127096398</v>
+        <v>127098060</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>98457</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529736</v>
+        <v>529843</v>
       </c>
       <c r="R2" t="n">
-        <v>6999860</v>
+        <v>6999863</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,11 +753,21 @@
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -760,26 +780,6 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -800,7 +800,7 @@
         <v>127098716</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -934,58 +934,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127098060</v>
+        <v>127096398</v>
       </c>
       <c r="B4" t="n">
-        <v>98488</v>
+        <v>79011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529843</v>
+        <v>529736</v>
       </c>
       <c r="R4" t="n">
-        <v>6999863</v>
+        <v>6999860</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,21 +1002,11 @@
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1039,6 +1019,26 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1059,7 +1059,7 @@
         <v>127098468</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>127099015</v>
       </c>
       <c r="B6" t="n">
-        <v>98488</v>
+        <v>98457</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>127098756</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>127097774</v>
       </c>
       <c r="B8" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>127098449</v>
       </c>
       <c r="B9" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>127096776</v>
       </c>
       <c r="B10" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>127099425</v>
       </c>
       <c r="B11" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>127172688</v>
       </c>
       <c r="B12" t="n">
-        <v>57832</v>
+        <v>57817</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>127172686</v>
       </c>
       <c r="B13" t="n">
-        <v>57832</v>
+        <v>57817</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>127172695</v>
       </c>
       <c r="B14" t="n">
-        <v>98468</v>
+        <v>98436</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>127172679</v>
       </c>
       <c r="B15" t="n">
-        <v>96720</v>
+        <v>96689</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>127172694</v>
       </c>
       <c r="B16" t="n">
-        <v>78787</v>
+        <v>78769</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>127172682</v>
       </c>
       <c r="B17" t="n">
-        <v>91350</v>
+        <v>91319</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>127172685</v>
       </c>
       <c r="B18" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>127172691</v>
       </c>
       <c r="B19" t="n">
-        <v>80161</v>
+        <v>80143</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>127172689</v>
       </c>
       <c r="B20" t="n">
-        <v>57832</v>
+        <v>57817</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>127172700</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>127172698</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3053,32 +3053,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127172678</v>
+        <v>127172696</v>
       </c>
       <c r="B23" t="n">
-        <v>75153</v>
+        <v>98436</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>529804</v>
+        <v>530028</v>
       </c>
       <c r="R23" t="n">
-        <v>6999861</v>
+        <v>6999912</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3150,32 +3150,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127172696</v>
+        <v>127172678</v>
       </c>
       <c r="B24" t="n">
-        <v>98468</v>
+        <v>75135</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>530028</v>
+        <v>529804</v>
       </c>
       <c r="R24" t="n">
-        <v>6999912</v>
+        <v>6999861</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3247,10 +3247,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127172687</v>
+        <v>127172684</v>
       </c>
       <c r="B25" t="n">
-        <v>57832</v>
+        <v>57657</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3258,34 +3258,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Södra Rörmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>530040</v>
+        <v>530054</v>
       </c>
       <c r="R25" t="n">
-        <v>6999850</v>
+        <v>6999817</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3318,6 +3326,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3347,7 +3360,7 @@
         <v>127172697</v>
       </c>
       <c r="B26" t="n">
-        <v>98468</v>
+        <v>98436</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3441,10 +3454,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127172684</v>
+        <v>127172687</v>
       </c>
       <c r="B27" t="n">
-        <v>57672</v>
+        <v>57817</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3452,42 +3465,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Södra Rörmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>530054</v>
+        <v>530040</v>
       </c>
       <c r="R27" t="n">
-        <v>6999817</v>
+        <v>6999850</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3520,11 +3525,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3554,7 +3554,7 @@
         <v>127172692</v>
       </c>
       <c r="B28" t="n">
-        <v>80132</v>
+        <v>80114</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3648,10 +3648,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127172693</v>
+        <v>127172680</v>
       </c>
       <c r="B29" t="n">
-        <v>78787</v>
+        <v>91319</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3659,21 +3659,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3683,10 +3683,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529977</v>
+        <v>529987</v>
       </c>
       <c r="R29" t="n">
-        <v>6999869</v>
+        <v>6999807</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3745,10 +3745,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127172680</v>
+        <v>127172693</v>
       </c>
       <c r="B30" t="n">
-        <v>91350</v>
+        <v>78769</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3756,21 +3756,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529987</v>
+        <v>529977</v>
       </c>
       <c r="R30" t="n">
-        <v>6999807</v>
+        <v>6999869</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3845,7 +3845,7 @@
         <v>127172701</v>
       </c>
       <c r="B31" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>127172681</v>
       </c>
       <c r="B32" t="n">
-        <v>91350</v>
+        <v>91319</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>127172699</v>
       </c>
       <c r="B33" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 32741-2025 artfynd.xlsx
+++ b/artfynd/A 32741-2025 artfynd.xlsx
@@ -675,58 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127098060</v>
+        <v>127096398</v>
       </c>
       <c r="B2" t="n">
-        <v>98457</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529843</v>
+        <v>529736</v>
       </c>
       <c r="R2" t="n">
-        <v>6999863</v>
+        <v>6999860</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,21 +743,11 @@
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -780,6 +760,26 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -800,7 +800,7 @@
         <v>127098716</v>
       </c>
       <c r="B3" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -934,48 +934,58 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127096398</v>
+        <v>127098060</v>
       </c>
       <c r="B4" t="n">
-        <v>79011</v>
+        <v>98488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529736</v>
+        <v>529843</v>
       </c>
       <c r="R4" t="n">
-        <v>6999860</v>
+        <v>6999863</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1002,11 +1012,21 @@
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1019,26 +1039,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1059,7 +1059,7 @@
         <v>127098468</v>
       </c>
       <c r="B5" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>127099015</v>
       </c>
       <c r="B6" t="n">
-        <v>98457</v>
+        <v>98488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>127098756</v>
       </c>
       <c r="B7" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>127097774</v>
       </c>
       <c r="B8" t="n">
-        <v>98436</v>
+        <v>98467</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>127098449</v>
       </c>
       <c r="B9" t="n">
-        <v>98436</v>
+        <v>98467</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>127096776</v>
       </c>
       <c r="B10" t="n">
-        <v>98436</v>
+        <v>98467</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>127099425</v>
       </c>
       <c r="B11" t="n">
-        <v>98436</v>
+        <v>98467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>127172688</v>
       </c>
       <c r="B12" t="n">
-        <v>57817</v>
+        <v>57832</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>127172686</v>
       </c>
       <c r="B13" t="n">
-        <v>57817</v>
+        <v>57832</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>127172695</v>
       </c>
       <c r="B14" t="n">
-        <v>98436</v>
+        <v>98468</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>127172679</v>
       </c>
       <c r="B15" t="n">
-        <v>96689</v>
+        <v>96720</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>127172694</v>
       </c>
       <c r="B16" t="n">
-        <v>78769</v>
+        <v>78787</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>127172682</v>
       </c>
       <c r="B17" t="n">
-        <v>91319</v>
+        <v>91350</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>127172685</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>57672</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>127172691</v>
       </c>
       <c r="B19" t="n">
-        <v>80143</v>
+        <v>80161</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>127172689</v>
       </c>
       <c r="B20" t="n">
-        <v>57817</v>
+        <v>57832</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>127172700</v>
       </c>
       <c r="B21" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>127172698</v>
       </c>
       <c r="B22" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3053,32 +3053,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127172696</v>
+        <v>127172678</v>
       </c>
       <c r="B23" t="n">
-        <v>98436</v>
+        <v>75153</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>530028</v>
+        <v>529804</v>
       </c>
       <c r="R23" t="n">
-        <v>6999912</v>
+        <v>6999861</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3150,32 +3150,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127172678</v>
+        <v>127172696</v>
       </c>
       <c r="B24" t="n">
-        <v>75135</v>
+        <v>98468</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529804</v>
+        <v>530028</v>
       </c>
       <c r="R24" t="n">
-        <v>6999861</v>
+        <v>6999912</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3247,10 +3247,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127172684</v>
+        <v>127172687</v>
       </c>
       <c r="B25" t="n">
-        <v>57657</v>
+        <v>57832</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3258,42 +3258,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Södra Rörmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>530054</v>
+        <v>530040</v>
       </c>
       <c r="R25" t="n">
-        <v>6999817</v>
+        <v>6999850</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3326,11 +3318,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3360,7 +3347,7 @@
         <v>127172697</v>
       </c>
       <c r="B26" t="n">
-        <v>98436</v>
+        <v>98468</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3454,10 +3441,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127172687</v>
+        <v>127172684</v>
       </c>
       <c r="B27" t="n">
-        <v>57817</v>
+        <v>57672</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,34 +3452,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Södra Rörmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>530040</v>
+        <v>530054</v>
       </c>
       <c r="R27" t="n">
-        <v>6999850</v>
+        <v>6999817</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3525,6 +3520,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3554,7 +3554,7 @@
         <v>127172692</v>
       </c>
       <c r="B28" t="n">
-        <v>80114</v>
+        <v>80132</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3648,10 +3648,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127172680</v>
+        <v>127172693</v>
       </c>
       <c r="B29" t="n">
-        <v>91319</v>
+        <v>78787</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3659,21 +3659,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3683,10 +3683,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529987</v>
+        <v>529977</v>
       </c>
       <c r="R29" t="n">
-        <v>6999807</v>
+        <v>6999869</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3745,10 +3745,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127172693</v>
+        <v>127172680</v>
       </c>
       <c r="B30" t="n">
-        <v>78769</v>
+        <v>91350</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3756,21 +3756,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529977</v>
+        <v>529987</v>
       </c>
       <c r="R30" t="n">
-        <v>6999869</v>
+        <v>6999807</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3845,7 +3845,7 @@
         <v>127172701</v>
       </c>
       <c r="B31" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>127172681</v>
       </c>
       <c r="B32" t="n">
-        <v>91319</v>
+        <v>91350</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>127172699</v>
       </c>
       <c r="B33" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 32741-2025 artfynd.xlsx
+++ b/artfynd/A 32741-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127096398</v>
+        <v>127172679</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Trättflon, Trättflon, Jmt</t>
+          <t>Södra Rörmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529736</v>
+        <v>530000</v>
       </c>
       <c r="R2" t="n">
-        <v>6999860</v>
+        <v>6999721</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,51 +756,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127098716</v>
+        <v>127172680</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Trättflon, Trättflon, Jmt</t>
+          <t>Södra Rörmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529925</v>
+        <v>529987</v>
       </c>
       <c r="R3" t="n">
-        <v>6999898</v>
+        <v>6999807</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,26 +840,11 @@
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -893,99 +853,64 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127098060</v>
+        <v>127172681</v>
       </c>
       <c r="B4" t="n">
-        <v>98488</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Trättflon, Trättflon, Jmt</t>
+          <t>Södra Rörmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529843</v>
+        <v>529827</v>
       </c>
       <c r="R4" t="n">
-        <v>6999863</v>
+        <v>6999866</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,21 +937,11 @@
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1035,31 +950,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127098468</v>
+        <v>127172682</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,37 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Trättflon, Trättflon, Jmt</t>
+          <t>Södra Rörmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529877</v>
+        <v>529798</v>
       </c>
       <c r="R5" t="n">
         <v>6999851</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1137,94 +1047,64 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127099015</v>
+        <v>127096398</v>
       </c>
       <c r="B6" t="n">
-        <v>98488</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529798</v>
+        <v>529736</v>
       </c>
       <c r="R6" t="n">
-        <v>6999885</v>
+        <v>6999860</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1251,21 +1131,11 @@
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1278,6 +1148,26 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1295,14 +1185,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127098756</v>
+        <v>127098468</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1330,13 +1220,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529874</v>
+        <v>529877</v>
       </c>
       <c r="R7" t="n">
-        <v>6999872</v>
+        <v>6999851</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1363,19 +1253,9 @@
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:10</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1427,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127097774</v>
+        <v>127098716</v>
       </c>
       <c r="B8" t="n">
-        <v>98467</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,53 +1318,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529828</v>
+        <v>529925</v>
       </c>
       <c r="R8" t="n">
-        <v>6999852</v>
+        <v>6999898</v>
       </c>
       <c r="S8" t="n">
         <v>9</v>
@@ -1516,7 +1377,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1526,12 +1387,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Minst 140 plantor och 6 blomstänglar och ett par vinterståndare inom ca 10 m2 yta.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1546,6 +1407,26 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1563,10 +1444,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127098449</v>
+        <v>127098731</v>
       </c>
       <c r="B9" t="n">
-        <v>98467</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,56 +1455,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529852</v>
+        <v>529890</v>
       </c>
       <c r="R9" t="n">
-        <v>6999838</v>
+        <v>6999898</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1652,7 +1514,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1662,12 +1524,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Minst 90 plantor inom ca 1 m2 yta.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1682,6 +1544,26 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1699,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127096776</v>
+        <v>127098756</v>
       </c>
       <c r="B10" t="n">
-        <v>98467</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1710,56 +1592,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529735</v>
+        <v>529874</v>
       </c>
       <c r="R10" t="n">
-        <v>6999871</v>
+        <v>6999872</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1788,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1798,12 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:02</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Minst 120 plantor inom ca 1,5 m2 yta.</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1818,6 +1676,26 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1835,10 +1713,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127099425</v>
+        <v>127172698</v>
       </c>
       <c r="B11" t="n">
-        <v>98467</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1846,57 +1724,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Trättflon, Trättflon, Jmt</t>
+          <t>Södra Rörmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529725</v>
+        <v>529927</v>
       </c>
       <c r="R11" t="n">
-        <v>6999846</v>
+        <v>6999903</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1923,82 +1781,61 @@
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Minst 5 plantor och 1 blomställning inom ca 0,5 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127172688</v>
+        <v>127172699</v>
       </c>
       <c r="B12" t="n">
-        <v>57832</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2008,10 +1845,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>530008</v>
+        <v>530016</v>
       </c>
       <c r="R12" t="n">
-        <v>6999777</v>
+        <v>6999865</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2070,32 +1907,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127172686</v>
+        <v>127172700</v>
       </c>
       <c r="B13" t="n">
-        <v>57832</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2105,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529974</v>
+        <v>530029</v>
       </c>
       <c r="R13" t="n">
-        <v>6999891</v>
+        <v>6999789</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2167,10 +2004,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127172695</v>
+        <v>127172701</v>
       </c>
       <c r="B14" t="n">
-        <v>98468</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2178,21 +2015,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2202,10 +2039,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529980</v>
+        <v>529845</v>
       </c>
       <c r="R14" t="n">
-        <v>6999916</v>
+        <v>6999850</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2264,10 +2101,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127172679</v>
+        <v>127172678</v>
       </c>
       <c r="B15" t="n">
-        <v>96720</v>
+        <v>83307</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2275,21 +2112,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2299,10 +2136,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>530000</v>
+        <v>529804</v>
       </c>
       <c r="R15" t="n">
-        <v>6999721</v>
+        <v>6999861</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2361,10 +2198,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127172694</v>
+        <v>127172693</v>
       </c>
       <c r="B16" t="n">
-        <v>78787</v>
+        <v>79084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2396,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529991</v>
+        <v>529977</v>
       </c>
       <c r="R16" t="n">
-        <v>6999806</v>
+        <v>6999869</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2458,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127172682</v>
+        <v>127172694</v>
       </c>
       <c r="B17" t="n">
-        <v>91350</v>
+        <v>79084</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2469,21 +2306,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2493,10 +2330,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529798</v>
+        <v>529991</v>
       </c>
       <c r="R17" t="n">
-        <v>6999851</v>
+        <v>6999806</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2555,10 +2392,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127172685</v>
+        <v>127172692</v>
       </c>
       <c r="B18" t="n">
-        <v>57672</v>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2566,42 +2403,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Södra Rörmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529946</v>
+        <v>529706</v>
       </c>
       <c r="R18" t="n">
-        <v>6999833</v>
+        <v>6999841</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2634,11 +2463,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2668,7 +2492,7 @@
         <v>127172691</v>
       </c>
       <c r="B19" t="n">
-        <v>80161</v>
+        <v>80461</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2762,10 +2586,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127172689</v>
+        <v>127172684</v>
       </c>
       <c r="B20" t="n">
-        <v>57832</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2773,34 +2597,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Södra Rörmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529921</v>
+        <v>530054</v>
       </c>
       <c r="R20" t="n">
-        <v>6999851</v>
+        <v>6999817</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2833,6 +2665,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2859,10 +2696,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127172700</v>
+        <v>127172685</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2870,34 +2707,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Södra Rörmyrhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>530029</v>
+        <v>529946</v>
       </c>
       <c r="R21" t="n">
-        <v>6999789</v>
+        <v>6999833</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2930,6 +2775,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2956,10 +2806,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127172698</v>
+        <v>124464827</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>58114</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2967,37 +2817,51 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Södra Rörmyrhöjden, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529927</v>
+        <v>529687</v>
       </c>
       <c r="R22" t="n">
-        <v>6999903</v>
+        <v>6999902</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3021,12 +2885,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>I flerskiktad äldre granskog med murkna björkhögstubbar för talltitans bohålsbygge.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3037,26 +2916,31 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127172678</v>
+        <v>127172686</v>
       </c>
       <c r="B23" t="n">
-        <v>75153</v>
+        <v>58114</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3064,21 +2948,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3088,10 +2972,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>529804</v>
+        <v>529974</v>
       </c>
       <c r="R23" t="n">
-        <v>6999861</v>
+        <v>6999891</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3150,32 +3034,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127172696</v>
+        <v>127172687</v>
       </c>
       <c r="B24" t="n">
-        <v>98468</v>
+        <v>58114</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3185,10 +3069,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>530028</v>
+        <v>530040</v>
       </c>
       <c r="R24" t="n">
-        <v>6999912</v>
+        <v>6999850</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3247,10 +3131,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127172687</v>
+        <v>127172688</v>
       </c>
       <c r="B25" t="n">
-        <v>57832</v>
+        <v>58114</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3282,10 +3166,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>530040</v>
+        <v>530008</v>
       </c>
       <c r="R25" t="n">
-        <v>6999850</v>
+        <v>6999777</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3344,32 +3228,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127172697</v>
+        <v>127172689</v>
       </c>
       <c r="B26" t="n">
-        <v>98468</v>
+        <v>58114</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3379,10 +3263,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>530041</v>
+        <v>529921</v>
       </c>
       <c r="R26" t="n">
-        <v>6999921</v>
+        <v>6999851</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3441,56 +3325,58 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127172684</v>
+        <v>127099591</v>
       </c>
       <c r="B27" t="n">
-        <v>57672</v>
+        <v>99035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Södra Rörmyrhöjden, Jmt</t>
+          <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>530054</v>
+        <v>529685</v>
       </c>
       <c r="R27" t="n">
-        <v>6999817</v>
+        <v>6999846</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3517,14 +3403,24 @@
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>I ett fuktstråk i äldre granskog.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3535,64 +3431,83 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127172692</v>
+        <v>124465010</v>
       </c>
       <c r="B28" t="n">
-        <v>80132</v>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Södra Rörmyrhöjden, Jmt</t>
+          <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529706</v>
+        <v>529689</v>
       </c>
       <c r="R28" t="n">
-        <v>6999841</v>
+        <v>6999902</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3616,12 +3531,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Minst 37 plantor och 3 vinterståndare inom ca 2 x 0,5 m2.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3632,61 +3562,85 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127172693</v>
+        <v>127096776</v>
       </c>
       <c r="B29" t="n">
-        <v>78787</v>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Södra Rörmyrhöjden, Jmt</t>
+          <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529977</v>
+        <v>529735</v>
       </c>
       <c r="R29" t="n">
-        <v>6999869</v>
+        <v>6999871</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3716,11 +3670,26 @@
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Minst 120 plantor inom ca 1,5 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3729,64 +3698,88 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127172680</v>
+        <v>127097774</v>
       </c>
       <c r="B30" t="n">
-        <v>91350</v>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Södra Rörmyrhöjden, Jmt</t>
+          <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529987</v>
+        <v>529828</v>
       </c>
       <c r="R30" t="n">
-        <v>6999807</v>
+        <v>6999852</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3813,11 +3806,26 @@
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Minst 140 plantor och 6 blomstänglar och ett par vinterståndare inom ca 10 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3826,61 +3834,85 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127172701</v>
+        <v>127098449</v>
       </c>
       <c r="B31" t="n">
-        <v>79029</v>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Södra Rörmyrhöjden, Jmt</t>
+          <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529845</v>
+        <v>529852</v>
       </c>
       <c r="R31" t="n">
-        <v>6999850</v>
+        <v>6999838</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3910,11 +3942,26 @@
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Minst 90 plantor inom ca 1 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3923,64 +3970,89 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127172681</v>
+        <v>127099425</v>
       </c>
       <c r="B32" t="n">
-        <v>91350</v>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Södra Rörmyrhöjden, Jmt</t>
+          <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>529827</v>
+        <v>529725</v>
       </c>
       <c r="R32" t="n">
-        <v>6999866</v>
+        <v>6999846</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4007,61 +4079,82 @@
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Minst 5 plantor och 1 blomställning inom ca 0,5 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127172699</v>
+        <v>127172695</v>
       </c>
       <c r="B33" t="n">
-        <v>79029</v>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4071,10 +4164,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>530016</v>
+        <v>529980</v>
       </c>
       <c r="R33" t="n">
-        <v>6999865</v>
+        <v>6999916</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4130,6 +4223,536 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>127172696</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Södra Rörmyrhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>530028</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6999912</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>127172697</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Södra Rörmyrhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>530041</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6999921</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>127098060</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Trättflon, Trättflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>529843</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6999863</v>
+      </c>
+      <c r="S36" t="n">
+        <v>9</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>127099015</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Trättflon, Trättflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>529798</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6999885</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>127172690</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Södra Rörmyrhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>530001</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6999721</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32741-2025 artfynd.xlsx
+++ b/artfynd/A 32741-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172679</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172680</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172681</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172682</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127096398</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127098468</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1441,6 +1476,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127098716</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1578,6 +1618,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127098731</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1710,6 +1755,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127098756</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1807,6 +1857,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172698</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1904,6 +1959,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172699</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2001,6 +2061,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172700</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2098,6 +2163,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172701</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2195,6 +2265,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172678</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2292,6 +2367,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172693</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2389,6 +2469,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172694</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2486,6 +2571,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172692</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2583,6 +2673,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172691</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2693,6 +2788,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172684</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2803,6 +2903,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172685</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2934,6 +3039,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124464827</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3031,6 +3141,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172686</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3128,6 +3243,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172687</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3225,6 +3345,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172688</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3322,6 +3447,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172689</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3449,6 +3579,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127099591</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3580,6 +3715,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124465010</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3716,6 +3856,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127096776</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3852,6 +3997,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127097774</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3988,6 +4138,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127098449</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4126,6 +4281,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127099425</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4223,6 +4383,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172695</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4320,6 +4485,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172696</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4417,6 +4587,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172697</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4539,6 +4714,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127098060</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4656,6 +4836,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127099015</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4753,8 +4938,52 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172690</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>